--- a/data/import/avery.xlsx
+++ b/data/import/avery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V271"/>
+  <dimension ref="A1:W271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>tds</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
